--- a/excel/nickname.xlsx
+++ b/excel/nickname.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gameSVN\game002\cocosProject\LieFlatGame\excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
@@ -10,7 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$610</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$608</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="105">
   <si>
     <t>编号【KEY】</t>
   </si>
@@ -45,12 +50,6 @@
   </si>
   <si>
     <t>string</t>
-  </si>
-  <si>
-    <t>server</t>
-  </si>
-  <si>
-    <t>client</t>
   </si>
   <si>
     <t>晚渡归舟</t>
@@ -363,7 +362,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -379,13 +378,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Microsoft YaHei"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
     </font>
@@ -534,7 +526,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -544,12 +536,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.149998474074526"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -879,52 +865,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -939,78 +928,75 @@
     <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1023,9 +1009,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1350,7 +1333,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C610"/>
+  <dimension ref="A1:C608"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="25.125" style="1" customWidth="1"/>
@@ -1385,25 +1368,25 @@
       </c>
       <c r="C3" s="4"/>
     </row>
-    <row r="4" ht="15" spans="1:3">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" s="4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" ht="15" spans="1:3">
-      <c r="A5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="5" t="s">
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="4">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -1411,7 +1394,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>8</v>
@@ -1419,7 +1402,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>9</v>
@@ -1427,7 +1410,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>10</v>
@@ -1435,7 +1418,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>11</v>
@@ -1443,7 +1426,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>12</v>
@@ -1451,7 +1434,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>13</v>
@@ -1459,7 +1442,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>14</v>
@@ -1467,7 +1450,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>15</v>
@@ -1475,7 +1458,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>16</v>
@@ -1483,7 +1466,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>17</v>
@@ -1491,7 +1474,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>18</v>
@@ -1499,7 +1482,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>19</v>
@@ -1507,7 +1490,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>20</v>
@@ -1515,7 +1498,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>21</v>
@@ -1523,7 +1506,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>22</v>
@@ -1531,7 +1514,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>23</v>
@@ -1539,7 +1522,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>24</v>
@@ -1547,7 +1530,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>25</v>
@@ -1555,7 +1538,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>26</v>
@@ -1563,7 +1546,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>27</v>
@@ -1571,7 +1554,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>28</v>
@@ -1579,7 +1562,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>29</v>
@@ -1587,7 +1570,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>30</v>
@@ -1595,7 +1578,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>31</v>
@@ -1603,7 +1586,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="4">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>32</v>
@@ -1611,7 +1594,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>33</v>
@@ -1619,7 +1602,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>34</v>
@@ -1627,7 +1610,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="4">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>35</v>
@@ -1635,7 +1618,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>36</v>
@@ -1643,7 +1626,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>37</v>
@@ -1651,7 +1634,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>38</v>
@@ -1659,7 +1642,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="4">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>39</v>
@@ -1667,7 +1650,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>40</v>
@@ -1675,7 +1658,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="4">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>41</v>
@@ -1683,7 +1666,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>42</v>
@@ -1691,7 +1674,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>43</v>
@@ -1699,7 +1682,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>44</v>
@@ -1707,7 +1690,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="4">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>45</v>
@@ -1715,7 +1698,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>46</v>
@@ -1723,7 +1706,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="4">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>47</v>
@@ -1731,7 +1714,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>48</v>
@@ -1739,7 +1722,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="4">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>49</v>
@@ -1747,7 +1730,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="4">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>50</v>
@@ -1755,7 +1738,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="4">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>51</v>
@@ -1763,7 +1746,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="4">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>52</v>
@@ -1771,7 +1754,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="4">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>53</v>
@@ -1779,7 +1762,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="4">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>54</v>
@@ -1787,7 +1770,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="4">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>55</v>
@@ -1795,7 +1778,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="4">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>56</v>
@@ -1803,7 +1786,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="4">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>57</v>
@@ -1811,7 +1794,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="4">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>58</v>
@@ -1819,7 +1802,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="4">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>59</v>
@@ -1827,7 +1810,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="4">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>60</v>
@@ -1835,7 +1818,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="4">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>61</v>
@@ -1843,7 +1826,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="4">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>62</v>
@@ -1851,7 +1834,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="4">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>63</v>
@@ -1859,7 +1842,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="4">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>64</v>
@@ -1867,7 +1850,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="4">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>65</v>
@@ -1875,7 +1858,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="4">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>66</v>
@@ -1883,7 +1866,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="4">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>67</v>
@@ -1891,7 +1874,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="4">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>68</v>
@@ -1899,7 +1882,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="4">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>69</v>
@@ -1907,7 +1890,7 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="4">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>70</v>
@@ -1915,7 +1898,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="4">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>71</v>
@@ -1923,7 +1906,7 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="4">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>72</v>
@@ -1931,7 +1914,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="4">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>73</v>
@@ -1939,7 +1922,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="4">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>74</v>
@@ -1947,7 +1930,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="4">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>75</v>
@@ -1955,7 +1938,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="4">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>76</v>
@@ -1963,7 +1946,7 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="4">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>77</v>
@@ -1971,7 +1954,7 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="4">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>78</v>
@@ -1979,7 +1962,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="4">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>79</v>
@@ -1987,7 +1970,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="4">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>80</v>
@@ -1995,7 +1978,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="4">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>81</v>
@@ -2003,7 +1986,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="4">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>82</v>
@@ -2011,7 +1994,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="4">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>83</v>
@@ -2019,7 +2002,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="4">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>84</v>
@@ -2027,7 +2010,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="4">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>85</v>
@@ -2035,7 +2018,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="4">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>86</v>
@@ -2043,7 +2026,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="4">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>87</v>
@@ -2051,7 +2034,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="4">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>88</v>
@@ -2059,7 +2042,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="4">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>89</v>
@@ -2067,7 +2050,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="4">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>90</v>
@@ -2075,7 +2058,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="4">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>91</v>
@@ -2083,7 +2066,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="4">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>92</v>
@@ -2091,7 +2074,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="4">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>93</v>
@@ -2099,7 +2082,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="4">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>94</v>
@@ -2107,7 +2090,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="4">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>95</v>
@@ -2115,7 +2098,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="4">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>96</v>
@@ -2123,7 +2106,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="4">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>97</v>
@@ -2131,7 +2114,7 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="4">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>98</v>
@@ -2139,7 +2122,7 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="4">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>99</v>
@@ -2147,7 +2130,7 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="4">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>100</v>
@@ -2155,15 +2138,16 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="4">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>101</v>
       </c>
+      <c r="C100" s="5"/>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="4">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>102</v>
@@ -2171,36 +2155,27 @@
     </row>
     <row r="102" spans="1:3">
       <c r="A102" s="4">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C102" s="6"/>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" s="4">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="4">
-        <v>99</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>105</v>
-      </c>
+      <c r="A104" s="4"/>
+      <c r="B104" s="4"/>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="4">
-        <v>100</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>106</v>
-      </c>
+      <c r="A105" s="4"/>
+      <c r="B105" s="4"/>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="4"/>
@@ -3572,55 +3547,53 @@
     </row>
     <row r="448" spans="1:2">
       <c r="A448" s="4"/>
-      <c r="B448" s="4"/>
-    </row>
-    <row r="449" spans="1:2">
+    </row>
+    <row r="449" spans="1:1">
       <c r="A449" s="4"/>
-      <c r="B449" s="4"/>
-    </row>
-    <row r="450" spans="1:2">
+    </row>
+    <row r="450" spans="1:1">
       <c r="A450" s="4"/>
     </row>
-    <row r="451" spans="1:2">
+    <row r="451" spans="1:1">
       <c r="A451" s="4"/>
     </row>
-    <row r="452" spans="1:2">
+    <row r="452" spans="1:1">
       <c r="A452" s="4"/>
     </row>
-    <row r="453" spans="1:2">
+    <row r="453" spans="1:1">
       <c r="A453" s="4"/>
     </row>
-    <row r="454" spans="1:2">
+    <row r="454" spans="1:1">
       <c r="A454" s="4"/>
     </row>
-    <row r="455" spans="1:2">
+    <row r="455" spans="1:1">
       <c r="A455" s="4"/>
     </row>
-    <row r="456" spans="1:2">
+    <row r="456" spans="1:1">
       <c r="A456" s="4"/>
     </row>
-    <row r="457" spans="1:2">
+    <row r="457" spans="1:1">
       <c r="A457" s="4"/>
     </row>
-    <row r="458" spans="1:2">
+    <row r="458" spans="1:1">
       <c r="A458" s="4"/>
     </row>
-    <row r="459" spans="1:2">
+    <row r="459" spans="1:1">
       <c r="A459" s="4"/>
     </row>
-    <row r="460" spans="1:2">
+    <row r="460" spans="1:1">
       <c r="A460" s="4"/>
     </row>
-    <row r="461" spans="1:2">
+    <row r="461" spans="1:1">
       <c r="A461" s="4"/>
     </row>
-    <row r="462" spans="1:2">
+    <row r="462" spans="1:1">
       <c r="A462" s="4"/>
     </row>
-    <row r="463" spans="1:2">
+    <row r="463" spans="1:1">
       <c r="A463" s="4"/>
     </row>
-    <row r="464" spans="1:2">
+    <row r="464" spans="1:1">
       <c r="A464" s="4"/>
     </row>
     <row r="465" spans="1:1">
@@ -4055,14 +4028,8 @@
     <row r="608" spans="1:1">
       <c r="A608" s="4"/>
     </row>
-    <row r="609" spans="1:1">
-      <c r="A609" s="4"/>
-    </row>
-    <row r="610" spans="1:1">
-      <c r="A610" s="4"/>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:B610" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:B608" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
